--- a/JIO/Cyntec/Cyntec_beam_table_v0.2.5.xlsx
+++ b/JIO/Cyntec/Cyntec_beam_table_v0.2.5.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="BeamTable" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="22">
   <si>
     <t xml:space="preserve">Beam Direction (deg)</t>
   </si>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t xml:space="preserve">X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spoiled Beam-BW=55</t>
   </si>
 </sst>
 </file>
@@ -599,7 +596,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>1</v>
@@ -3982,8 +3979,8 @@
       <c r="B47" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>22</v>
+      <c r="C47" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>0</v>

--- a/JIO/Cyntec/Cyntec_beam_table_v0.2.5.xlsx
+++ b/JIO/Cyntec/Cyntec_beam_table_v0.2.5.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="BeamTable" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="23">
   <si>
     <t xml:space="preserve">Beam Direction (deg)</t>
   </si>
@@ -50,6 +50,9 @@
     <t xml:space="preserve">1,2,3,4</t>
   </si>
   <si>
+    <t xml:space="preserve">narrow</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,2,4</t>
   </si>
   <si>
@@ -59,10 +62,10 @@
     <t xml:space="preserve">1,2,3</t>
   </si>
   <si>
-    <t xml:space="preserve">Spoiled Beam</t>
+    <t xml:space="preserve">Spoiled</t>
   </si>
   <si>
-    <t xml:space="preserve">Tri Beam</t>
+    <t xml:space="preserve">Tri</t>
   </si>
   <si>
     <t xml:space="preserve">Element Map</t>
@@ -593,10 +596,13 @@
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
+      <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>1</v>
@@ -609,10 +615,13 @@
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
+      <c r="G4" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>2</v>
@@ -625,10 +634,13 @@
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>3</v>
@@ -641,10 +653,13 @@
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
+      <c r="G6" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>4</v>
@@ -657,10 +672,13 @@
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
+      <c r="G7" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>5</v>
@@ -673,10 +691,13 @@
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
+      <c r="G8" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>6</v>
@@ -689,10 +710,13 @@
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
+      <c r="G9" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>7</v>
@@ -705,10 +729,13 @@
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
+      <c r="G10" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>8</v>
@@ -721,10 +748,13 @@
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
+      <c r="G11" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>9</v>
@@ -737,10 +767,13 @@
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
+      <c r="G12" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>10</v>
@@ -753,10 +786,13 @@
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
+      <c r="G13" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>11</v>
@@ -769,10 +805,13 @@
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
+      <c r="G14" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" s="6" t="n">
         <v>12</v>
@@ -785,10 +824,13 @@
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
+      <c r="G15" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" s="6" t="n">
         <v>13</v>
@@ -801,10 +843,13 @@
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
+      <c r="G16" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" s="6" t="n">
         <v>14</v>
@@ -817,10 +862,13 @@
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
+      <c r="G17" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18" s="6" t="n">
         <v>15</v>
@@ -833,10 +881,13 @@
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
+      <c r="G18" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19" s="6" t="n">
         <v>16</v>
@@ -849,10 +900,13 @@
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
+      <c r="G19" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20" s="6" t="n">
         <v>17</v>
@@ -865,10 +919,13 @@
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
+      <c r="G20" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21" s="6" t="n">
         <v>18</v>
@@ -881,10 +938,13 @@
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
+      <c r="G21" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B22" s="6" t="n">
         <v>19</v>
@@ -897,10 +957,13 @@
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
+      <c r="G22" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B23" s="6" t="n">
         <v>20</v>
@@ -913,10 +976,13 @@
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
+      <c r="G23" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>21</v>
@@ -929,10 +995,13 @@
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
+      <c r="G24" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B25" s="4" t="n">
         <v>22</v>
@@ -945,10 +1014,13 @@
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
+      <c r="G25" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B26" s="4" t="n">
         <v>23</v>
@@ -961,10 +1033,13 @@
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
+      <c r="G26" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B27" s="4" t="n">
         <v>24</v>
@@ -977,10 +1052,13 @@
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
+      <c r="G27" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>25</v>
@@ -993,10 +1071,13 @@
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
+      <c r="G28" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>26</v>
@@ -1009,10 +1090,13 @@
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
+      <c r="G29" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>27</v>
@@ -1025,10 +1109,13 @@
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
+      <c r="G30" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>28</v>
@@ -1041,10 +1128,13 @@
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
+      <c r="G31" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>29</v>
@@ -1057,10 +1147,13 @@
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
+      <c r="G32" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>30</v>
@@ -1073,10 +1166,13 @@
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
+      <c r="G33" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>31</v>
@@ -1089,10 +1185,13 @@
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
+      <c r="G34" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B35" s="7" t="n">
         <v>32</v>
@@ -1105,10 +1204,13 @@
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
+      <c r="G35" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B36" s="7" t="n">
         <v>33</v>
@@ -1121,10 +1223,13 @@
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
+      <c r="G36" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B37" s="7" t="n">
         <v>34</v>
@@ -1137,10 +1242,13 @@
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
+      <c r="G37" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B38" s="7" t="n">
         <v>35</v>
@@ -1153,10 +1261,13 @@
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
+      <c r="G38" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B39" s="7" t="n">
         <v>36</v>
@@ -1169,10 +1280,13 @@
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
+      <c r="G39" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B40" s="7" t="n">
         <v>37</v>
@@ -1185,10 +1299,13 @@
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
+      <c r="G40" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B41" s="7" t="n">
         <v>38</v>
@@ -1201,10 +1318,13 @@
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
+      <c r="G41" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B42" s="7" t="n">
         <v>39</v>
@@ -1217,10 +1337,13 @@
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
+      <c r="G42" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B43" s="7" t="n">
         <v>40</v>
@@ -1233,10 +1356,13 @@
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
+      <c r="G43" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B44" s="7" t="n">
         <v>41</v>
@@ -1249,10 +1375,13 @@
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
+      <c r="G44" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B45" s="4" t="n">
         <v>42</v>
@@ -1265,10 +1394,13 @@
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
+      <c r="G45" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B46" s="4" t="n">
         <v>43</v>
@@ -1281,10 +1413,13 @@
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
+      <c r="G46" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B47" s="4" t="n">
         <v>44</v>
@@ -1297,10 +1432,13 @@
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
+      <c r="G47" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B48" s="4" t="n">
         <v>45</v>
@@ -1313,10 +1451,13 @@
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
+      <c r="G48" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B49" s="4" t="n">
         <v>46</v>
@@ -1329,10 +1470,13 @@
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
+      <c r="G49" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B50" s="4" t="n">
         <v>47</v>
@@ -1345,10 +1489,13 @@
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
+      <c r="G50" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B51" s="4" t="n">
         <v>48</v>
@@ -1361,10 +1508,13 @@
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
+      <c r="G51" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B52" s="4" t="n">
         <v>49</v>
@@ -1377,10 +1527,13 @@
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
+      <c r="G52" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B53" s="4" t="n">
         <v>50</v>
@@ -1393,10 +1546,13 @@
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
+      <c r="G53" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B54" s="4" t="n">
         <v>51</v>
@@ -1409,10 +1565,13 @@
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
+      <c r="G54" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B55" s="4" t="n">
         <v>52</v>
@@ -1425,10 +1584,13 @@
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
+      <c r="G55" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B56" s="6" t="n">
         <v>53</v>
@@ -1441,10 +1603,13 @@
       </c>
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
+      <c r="G56" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B57" s="6" t="n">
         <v>54</v>
@@ -1457,10 +1622,13 @@
       </c>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
+      <c r="G57" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58" s="6" t="n">
         <v>55</v>
@@ -1473,10 +1641,13 @@
       </c>
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
+      <c r="G58" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B59" s="6" t="n">
         <v>56</v>
@@ -1489,10 +1660,13 @@
       </c>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
+      <c r="G59" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B60" s="6" t="n">
         <v>57</v>
@@ -1505,10 +1679,13 @@
       </c>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
+      <c r="G60" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B61" s="6" t="n">
         <v>58</v>
@@ -1521,10 +1698,13 @@
       </c>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
+      <c r="G61" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B62" s="6" t="n">
         <v>59</v>
@@ -1537,10 +1717,13 @@
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
+      <c r="G62" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B63" s="6" t="n">
         <v>60</v>
@@ -1553,10 +1736,13 @@
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
+      <c r="G63" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B64" s="6" t="n">
         <v>61</v>
@@ -1569,10 +1755,13 @@
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
+      <c r="G64" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B65" s="6" t="n">
         <v>62</v>
@@ -1585,10 +1774,13 @@
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
+      <c r="G65" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B66" s="4" t="n">
         <v>63</v>
@@ -1601,10 +1793,13 @@
       </c>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
+      <c r="G66" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B67" s="4" t="n">
         <v>64</v>
@@ -1617,10 +1812,13 @@
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
+      <c r="G67" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B68" s="4" t="n">
         <v>65</v>
@@ -1633,10 +1831,13 @@
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
+      <c r="G68" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B69" s="4" t="n">
         <v>66</v>
@@ -1649,10 +1850,13 @@
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
+      <c r="G69" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B70" s="4" t="n">
         <v>67</v>
@@ -1665,10 +1869,13 @@
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
+      <c r="G70" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B71" s="4" t="n">
         <v>68</v>
@@ -1681,10 +1888,13 @@
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
+      <c r="G71" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B72" s="4" t="n">
         <v>69</v>
@@ -1697,10 +1907,13 @@
       </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
+      <c r="G72" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B73" s="4" t="n">
         <v>70</v>
@@ -1713,10 +1926,13 @@
       </c>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
+      <c r="G73" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B74" s="4" t="n">
         <v>71</v>
@@ -1729,10 +1945,13 @@
       </c>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
+      <c r="G74" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B75" s="4" t="n">
         <v>72</v>
@@ -1745,10 +1964,13 @@
       </c>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
+      <c r="G75" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B76" s="7" t="n">
         <v>73</v>
@@ -1761,10 +1983,13 @@
       </c>
       <c r="E76" s="7"/>
       <c r="F76" s="7"/>
+      <c r="G76" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B77" s="7" t="n">
         <v>74</v>
@@ -1777,10 +2002,13 @@
       </c>
       <c r="E77" s="7"/>
       <c r="F77" s="7"/>
+      <c r="G77" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B78" s="7" t="n">
         <v>75</v>
@@ -1793,10 +2021,13 @@
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="7"/>
+      <c r="G78" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B79" s="7" t="n">
         <v>76</v>
@@ -1809,10 +2040,13 @@
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="7"/>
+      <c r="G79" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B80" s="7" t="n">
         <v>77</v>
@@ -1825,10 +2059,13 @@
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="7"/>
+      <c r="G80" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B81" s="7" t="n">
         <v>78</v>
@@ -1841,10 +2078,13 @@
       </c>
       <c r="E81" s="7"/>
       <c r="F81" s="7"/>
+      <c r="G81" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B82" s="7" t="n">
         <v>79</v>
@@ -1857,10 +2097,13 @@
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
+      <c r="G82" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B83" s="7" t="n">
         <v>80</v>
@@ -1873,10 +2116,13 @@
       </c>
       <c r="E83" s="7"/>
       <c r="F83" s="7"/>
+      <c r="G83" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B84" s="7" t="n">
         <v>81</v>
@@ -1889,10 +2135,13 @@
       </c>
       <c r="E84" s="7"/>
       <c r="F84" s="7"/>
+      <c r="G84" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B85" s="7" t="n">
         <v>82</v>
@@ -1905,10 +2154,13 @@
       </c>
       <c r="E85" s="7"/>
       <c r="F85" s="7"/>
+      <c r="G85" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B86" s="7" t="n">
         <v>83</v>
@@ -1921,10 +2173,13 @@
       </c>
       <c r="E86" s="7"/>
       <c r="F86" s="7"/>
+      <c r="G86" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B87" s="4" t="n">
         <v>84</v>
@@ -1937,10 +2192,13 @@
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
+      <c r="G87" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B88" s="4" t="n">
         <v>85</v>
@@ -1953,10 +2211,13 @@
       </c>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
+      <c r="G88" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B89" s="4" t="n">
         <v>86</v>
@@ -1969,10 +2230,13 @@
       </c>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
+      <c r="G89" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B90" s="4" t="n">
         <v>87</v>
@@ -1985,10 +2249,13 @@
       </c>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
+      <c r="G90" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B91" s="4" t="n">
         <v>88</v>
@@ -2001,10 +2268,13 @@
       </c>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
+      <c r="G91" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B92" s="4" t="n">
         <v>89</v>
@@ -2017,10 +2287,13 @@
       </c>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
+      <c r="G92" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B93" s="4" t="n">
         <v>90</v>
@@ -2033,10 +2306,13 @@
       </c>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
+      <c r="G93" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B94" s="4" t="n">
         <v>91</v>
@@ -2049,10 +2325,13 @@
       </c>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
+      <c r="G94" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B95" s="4" t="n">
         <v>92</v>
@@ -2065,10 +2344,13 @@
       </c>
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
+      <c r="G95" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B96" s="4" t="n">
         <v>93</v>
@@ -2081,10 +2363,13 @@
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
+      <c r="G96" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B97" s="4" t="n">
         <v>94</v>
@@ -2097,6 +2382,9 @@
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
+      <c r="G97" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="n">
@@ -2118,7 +2406,7 @@
         <v>11.3</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2141,7 +2429,7 @@
         <v>11.29</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2164,7 +2452,7 @@
         <v>11.28</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2187,7 +2475,7 @@
         <v>30</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2210,7 +2498,7 @@
         <v>30</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2233,7 +2521,7 @@
         <v>30</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2270,10 +2558,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
@@ -2282,31 +2570,31 @@
         <v>6</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R1" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2321,28 +2609,28 @@
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N2" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O2" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P2" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R2" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2350,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>0</v>
@@ -2363,28 +2651,28 @@
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2392,7 +2680,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="8" t="n">
         <v>0</v>
@@ -2405,28 +2693,28 @@
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2434,7 +2722,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>0</v>
@@ -2447,28 +2735,28 @@
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2476,7 +2764,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>0</v>
@@ -2489,28 +2777,28 @@
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R6" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2518,7 +2806,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>1.5</v>
@@ -2531,28 +2819,28 @@
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2560,7 +2848,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>1.5</v>
@@ -2573,28 +2861,28 @@
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L8" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R8" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2602,7 +2890,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>1.5</v>
@@ -2614,31 +2902,31 @@
         <v>11.26</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R9" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2646,7 +2934,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>1.5</v>
@@ -2659,28 +2947,28 @@
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N10" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P10" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q10" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R10" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2688,7 +2976,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>3</v>
@@ -2701,28 +2989,28 @@
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O11" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q11" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R11" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2730,7 +3018,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>3</v>
@@ -2743,28 +3031,28 @@
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M12" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O12" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P12" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q12" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R12" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2772,7 +3060,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>3</v>
@@ -2785,28 +3073,28 @@
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M13" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O13" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P13" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q13" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R13" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2814,7 +3102,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>3</v>
@@ -2827,28 +3115,28 @@
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M14" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N14" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q14" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R14" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2856,7 +3144,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>4.5</v>
@@ -2869,28 +3157,28 @@
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N15" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O15" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q15" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R15" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2898,7 +3186,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>4.5</v>
@@ -2911,28 +3199,28 @@
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L16" s="26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M16" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q16" s="26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R16" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2940,7 +3228,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>4.5</v>
@@ -2952,31 +3240,31 @@
         <v>11.26</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M17" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P17" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R17" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2984,7 +3272,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>4.5</v>
@@ -2997,28 +3285,28 @@
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M18" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N18" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O18" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P18" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q18" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R18" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3026,7 +3314,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>6</v>
@@ -3039,28 +3327,28 @@
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M19" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N19" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O19" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P19" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q19" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R19" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3068,7 +3356,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>6</v>
@@ -3081,28 +3369,28 @@
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M20" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N20" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P20" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q20" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R20" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3110,7 +3398,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>6</v>
@@ -3123,28 +3411,28 @@
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M21" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O21" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P21" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q21" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R21" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3152,7 +3440,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>6</v>
@@ -3165,28 +3453,28 @@
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N22" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O22" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P22" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q22" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R22" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3194,7 +3482,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>7.5</v>
@@ -3207,28 +3495,28 @@
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N23" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O23" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P23" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q23" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R23" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3236,7 +3524,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>7.5</v>
@@ -3249,28 +3537,28 @@
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L24" s="26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M24" s="26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O24" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P24" s="26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q24" s="26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R24" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3278,7 +3566,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>7.5</v>
@@ -3290,31 +3578,31 @@
         <v>11.26</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K25" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L25" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M25" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O25" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P25" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q25" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R25" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3322,7 +3610,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>7.5</v>
@@ -3335,28 +3623,28 @@
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N26" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O26" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P26" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q26" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R26" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3364,7 +3652,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>9</v>
@@ -3377,28 +3665,28 @@
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M27" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N27" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O27" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P27" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q27" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R27" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3406,7 +3694,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>9</v>
@@ -3419,28 +3707,28 @@
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M28" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N28" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O28" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P28" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q28" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R28" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3448,7 +3736,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>9</v>
@@ -3461,28 +3749,28 @@
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M29" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N29" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O29" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P29" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q29" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R29" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3490,7 +3778,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>9</v>
@@ -3503,28 +3791,28 @@
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M30" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N30" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O30" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P30" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q30" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R30" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3532,7 +3820,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>10.5</v>
@@ -3545,28 +3833,28 @@
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L31" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M31" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O31" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P31" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q31" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R31" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3574,7 +3862,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>10.5</v>
@@ -3587,28 +3875,28 @@
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L32" s="26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M32" s="26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N32" s="26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O32" s="26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P32" s="26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q32" s="26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R32" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3616,7 +3904,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>10.5</v>
@@ -3642,7 +3930,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>10.5</v>
@@ -3668,7 +3956,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>12</v>
@@ -3694,7 +3982,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>12</v>
@@ -3720,7 +4008,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>12</v>
@@ -3746,7 +4034,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>12</v>
@@ -3772,7 +4060,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>13.5</v>
@@ -3798,7 +4086,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>13.5</v>
@@ -3824,7 +4112,7 @@
         <v>39</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>13.5</v>
@@ -3850,7 +4138,7 @@
         <v>40</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D42" s="8" t="n">
         <v>13.5</v>
@@ -3876,7 +4164,7 @@
         <v>41</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>15</v>
@@ -3902,7 +4190,7 @@
         <v>42</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>15</v>
@@ -3928,7 +4216,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>15</v>
@@ -3954,7 +4242,7 @@
         <v>44</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>15</v>
@@ -3980,7 +4268,7 @@
         <v>45</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>0</v>

--- a/JIO/Cyntec/Cyntec_beam_table_v0.2.5.xlsx
+++ b/JIO/Cyntec/Cyntec_beam_table_v0.2.5.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">1,2,3,4</t>
   </si>
   <si>
-    <t xml:space="preserve">narrow</t>
+    <t xml:space="preserve">Narrow</t>
   </si>
   <si>
     <t xml:space="preserve">1,2,4</t>
